--- a/赵弘远同志历年荣誉表彰汇总.xlsx
+++ b/赵弘远同志历年荣誉表彰汇总.xlsx
@@ -74,7 +74,7 @@
     <t>市级表彰（拟表彰）</t>
   </si>
   <si>
-    <t>邺山村优秀邺年</t>
+    <t>邺山村优秀青年</t>
   </si>
   <si>
     <t>邺山村村民委员会</t>
@@ -113,7 +113,7 @@
     <t>县级表彰</t>
   </si>
   <si>
-    <t>乡村振兴优秀邺年志愿者</t>
+    <t>乡村振兴优秀青年志愿者</t>
   </si>
   <si>
     <t>县级乡村振兴局</t>
